--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90222</v>
+        <v>90232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90222</v>
+        <v>90232</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90232</v>
+        <v>90244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90232</v>
+        <v>90244</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90244</v>
+        <v>90245</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90244</v>
+        <v>90245</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90245</v>
+        <v>90248</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90245</v>
+        <v>90248</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90248</v>
+        <v>90254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90248</v>
+        <v>90254</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>112194201</v>
       </c>
       <c r="B5" t="n">
-        <v>90255</v>
+        <v>90262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>112194202</v>
       </c>
       <c r="B42" t="n">
-        <v>90255</v>
+        <v>90262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>67082906</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518143.5614963392</v>
+        <v>518144</v>
       </c>
       <c r="R2" t="n">
-        <v>7087552.279335845</v>
+        <v>7087552</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112194191</v>
+        <v>67082927</v>
       </c>
       <c r="B3" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,41 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518083</v>
+        <v>518289</v>
       </c>
       <c r="R3" t="n">
-        <v>7087574</v>
+        <v>7087460</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112194209</v>
+        <v>67082938</v>
       </c>
       <c r="B4" t="n">
-        <v>89610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518114</v>
+        <v>518471</v>
       </c>
       <c r="R4" t="n">
-        <v>7087489</v>
+        <v>7087324</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,65 +962,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112194201</v>
+        <v>67082944</v>
       </c>
       <c r="B5" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5747</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518167</v>
+        <v>518333</v>
       </c>
       <c r="R5" t="n">
-        <v>7087545</v>
+        <v>7087491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,70 +1043,68 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112194182</v>
+        <v>112194213</v>
       </c>
       <c r="B6" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>1599</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518134</v>
+        <v>518125</v>
       </c>
       <c r="R6" t="n">
-        <v>7087528</v>
+        <v>7087460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,8 +1156,9 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,15 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112194181</v>
+        <v>112194211</v>
       </c>
       <c r="B7" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518119</v>
+        <v>518132</v>
       </c>
       <c r="R7" t="n">
-        <v>7087546</v>
+        <v>7087535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112194205</v>
+        <v>67082909</v>
       </c>
       <c r="B8" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1285,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518193</v>
+        <v>518204</v>
       </c>
       <c r="R8" t="n">
-        <v>7087437</v>
+        <v>7087395</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,27 +1359,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112194180</v>
+        <v>67082930</v>
       </c>
       <c r="B9" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,37 +1386,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518125</v>
+        <v>518345</v>
       </c>
       <c r="R9" t="n">
-        <v>7087474</v>
+        <v>7087388</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,12 +1440,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,27 +1460,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112194188</v>
+        <v>112194175</v>
       </c>
       <c r="B10" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,38 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518083</v>
+        <v>518455</v>
       </c>
       <c r="R10" t="n">
-        <v>7087539</v>
+        <v>7087371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,53 +1573,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112194212</v>
+        <v>112194176</v>
       </c>
       <c r="B11" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518174</v>
+        <v>518411</v>
       </c>
       <c r="R11" t="n">
-        <v>7087423</v>
+        <v>7087343</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1652,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1732,15 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112194189</v>
+        <v>112194177</v>
       </c>
       <c r="B12" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,38 +1681,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518073</v>
+        <v>518335</v>
       </c>
       <c r="R12" t="n">
-        <v>7087552</v>
+        <v>7087446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1741,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,15 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112194183</v>
+        <v>112194178</v>
       </c>
       <c r="B13" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518177</v>
+        <v>518293</v>
       </c>
       <c r="R13" t="n">
-        <v>7087545</v>
+        <v>7087436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,15 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112194210</v>
+        <v>112194179</v>
       </c>
       <c r="B14" t="n">
-        <v>89610</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1961,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518178</v>
+        <v>518215</v>
       </c>
       <c r="R14" t="n">
-        <v>7087549</v>
+        <v>7087400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,15 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112194211</v>
+        <v>112194180</v>
       </c>
       <c r="B15" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518132</v>
+        <v>518124</v>
       </c>
       <c r="R15" t="n">
-        <v>7087535</v>
+        <v>7087474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,37 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112194213</v>
+        <v>112194181</v>
       </c>
       <c r="B16" t="n">
-        <v>88220</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1599</v>
+        <v>4412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518125</v>
+        <v>518119</v>
       </c>
       <c r="R16" t="n">
-        <v>7087460</v>
+        <v>7087546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,9 +2135,8 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2252,15 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112194190</v>
+        <v>112194182</v>
       </c>
       <c r="B17" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,38 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518066</v>
+        <v>518134</v>
       </c>
       <c r="R17" t="n">
-        <v>7087556</v>
+        <v>7087528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,37 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112194199</v>
+        <v>112194183</v>
       </c>
       <c r="B18" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>4412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518127</v>
+        <v>518177</v>
       </c>
       <c r="R18" t="n">
-        <v>7087447</v>
+        <v>7087544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,15 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112194192</v>
+        <v>112194184</v>
       </c>
       <c r="B19" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,38 +2360,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518091</v>
+        <v>518228</v>
       </c>
       <c r="R19" t="n">
-        <v>7087574</v>
+        <v>7087545</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,53 +2446,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67082940</v>
+        <v>112194199</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518364.9304356659</v>
+        <v>518127</v>
       </c>
       <c r="R20" t="n">
-        <v>7087456.73341616</v>
+        <v>7087447</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,22 +2511,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2676,69 +2531,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67082941</v>
+        <v>112194201</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5747</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518335.1975777112</v>
+        <v>518167</v>
       </c>
       <c r="R21" t="n">
-        <v>7087491.332742036</v>
+        <v>7087545</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2762,99 +2608,81 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67082927</v>
+        <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518288.6629372206</v>
+        <v>518255</v>
       </c>
       <c r="R22" t="n">
-        <v>7087459.808235356</v>
+        <v>7087576</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2878,22 +2706,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,31 +2726,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67082942</v>
+        <v>112194212</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,37 +2749,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518335.1975777112</v>
+        <v>518174</v>
       </c>
       <c r="R23" t="n">
-        <v>7087491.332742036</v>
+        <v>7087422</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2994,22 +2806,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,59 +2820,51 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67082945</v>
+        <v>67082905</v>
       </c>
       <c r="B24" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518335.1975777112</v>
+        <v>518259</v>
       </c>
       <c r="R24" t="n">
-        <v>7087491.332742036</v>
+        <v>7087612</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3113,19 +2907,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,37 +2940,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67082938</v>
+        <v>67082908</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,10 +2975,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518471.4961736461</v>
+        <v>518207</v>
       </c>
       <c r="R25" t="n">
-        <v>7087323.544370682</v>
+        <v>7087393</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3229,19 +3008,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,32 +3041,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67082911</v>
+        <v>67082933</v>
       </c>
       <c r="B26" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3312,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518204.9283606771</v>
+        <v>518344</v>
       </c>
       <c r="R26" t="n">
-        <v>7087382.728766739</v>
+        <v>7087387</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3345,19 +3109,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,37 +3142,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67082910</v>
+        <v>67082936</v>
       </c>
       <c r="B27" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3428,10 +3177,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518204.902758911</v>
+        <v>518443</v>
       </c>
       <c r="R27" t="n">
-        <v>7087387.130467622</v>
+        <v>7087315</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3461,19 +3210,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,37 +3243,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67082907</v>
+        <v>67082942</v>
       </c>
       <c r="B28" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3544,10 +3278,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518204.902758911</v>
+        <v>518335</v>
       </c>
       <c r="R28" t="n">
-        <v>7087387.130467622</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3577,19 +3311,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3620,15 +3344,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67082943</v>
+        <v>67082907</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3636,21 +3355,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3660,10 +3379,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518335.1975777112</v>
+        <v>518205</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491.332742036</v>
+        <v>7087387</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3693,19 +3412,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,15 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67082909</v>
+        <v>67082929</v>
       </c>
       <c r="B30" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,21 +3456,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3776,10 +3480,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518203.5344489382</v>
+        <v>518349</v>
       </c>
       <c r="R30" t="n">
-        <v>7087395.045823406</v>
+        <v>7087389</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3809,19 +3513,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,15 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67082936</v>
+        <v>67082940</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3868,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3892,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518443.3372989752</v>
+        <v>518365</v>
       </c>
       <c r="R31" t="n">
-        <v>7087315.014623537</v>
+        <v>7087457</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3925,19 +3614,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,15 +3647,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67082944</v>
+        <v>112194203</v>
       </c>
       <c r="B32" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,37 +3658,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518333.434662688</v>
+        <v>518417</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491.322415015</v>
+        <v>7087421</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4038,22 +3712,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4068,31 +3732,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67082908</v>
+        <v>112194204</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4100,37 +3755,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518206.6324470416</v>
+        <v>518351</v>
       </c>
       <c r="R33" t="n">
-        <v>7087392.862924065</v>
+        <v>7087447</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4154,22 +3809,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,69 +3829,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67082926</v>
+        <v>112194205</v>
       </c>
       <c r="B34" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brännbodarna, Jmt</t>
+          <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518268.83508197</v>
+        <v>518193</v>
       </c>
       <c r="R34" t="n">
-        <v>7087458.812089412</v>
+        <v>7087437</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4270,22 +3906,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4300,31 +3926,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67082937</v>
+        <v>67082910</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4332,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4356,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518443.3372989752</v>
+        <v>518205</v>
       </c>
       <c r="R35" t="n">
-        <v>7087315.014623537</v>
+        <v>7087387</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4389,19 +4006,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,37 +4039,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67082946</v>
+        <v>67082932</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4472,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518282.1672112891</v>
+        <v>518344</v>
       </c>
       <c r="R36" t="n">
-        <v>7087590.939582426</v>
+        <v>7087387</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4505,19 +4107,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4548,53 +4140,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112194178</v>
+        <v>67082941</v>
       </c>
       <c r="B37" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518293</v>
+        <v>518335</v>
       </c>
       <c r="R37" t="n">
-        <v>7087436</v>
+        <v>7087491</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4618,12 +4205,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,69 +4225,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112194187</v>
+        <v>67082911</v>
       </c>
       <c r="B38" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518287</v>
+        <v>518205</v>
       </c>
       <c r="R38" t="n">
-        <v>7087594</v>
+        <v>7087383</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4724,17 +4306,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4749,65 +4326,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112194176</v>
+        <v>67082928</v>
       </c>
       <c r="B39" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518411</v>
+        <v>518353</v>
       </c>
       <c r="R39" t="n">
-        <v>7087343</v>
+        <v>7087386</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4831,12 +4407,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4851,65 +4427,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112194208</v>
+        <v>67082945</v>
       </c>
       <c r="B40" t="n">
-        <v>89610</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518398</v>
+        <v>518335</v>
       </c>
       <c r="R40" t="n">
-        <v>7087385</v>
+        <v>7087491</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4933,12 +4508,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4953,27 +4528,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112194177</v>
+        <v>67082904</v>
       </c>
       <c r="B41" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4981,37 +4555,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518335</v>
+        <v>518277</v>
       </c>
       <c r="R41" t="n">
-        <v>7087446</v>
+        <v>7087637</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5035,12 +4609,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5055,65 +4629,64 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112194202</v>
+        <v>67082946</v>
       </c>
       <c r="B42" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>laholmsnäset, Jmt</t>
+          <t>Brännbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518255</v>
+        <v>518282</v>
       </c>
       <c r="R42" t="n">
-        <v>7087576</v>
+        <v>7087591</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,12 +4710,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,27 +4730,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112194184</v>
+        <v>112194187</v>
       </c>
       <c r="B43" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5185,34 +4757,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518228</v>
+        <v>518287</v>
       </c>
       <c r="R43" t="n">
-        <v>7087545</v>
+        <v>7087594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5245,6 +4821,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5271,15 +4852,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112194193</v>
+        <v>112194188</v>
       </c>
       <c r="B44" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5315,10 +4891,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518252</v>
+        <v>518083</v>
       </c>
       <c r="R44" t="n">
-        <v>7087575</v>
+        <v>7087539</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,7 +4931,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,15 +4958,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112194203</v>
+        <v>112194189</v>
       </c>
       <c r="B45" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5398,34 +4969,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518417</v>
+        <v>518072</v>
       </c>
       <c r="R45" t="n">
-        <v>7087421</v>
+        <v>7087552</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5458,6 +5033,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5484,15 +5064,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112194194</v>
+        <v>112194190</v>
       </c>
       <c r="B46" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5528,10 +5103,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518245</v>
+        <v>518067</v>
       </c>
       <c r="R46" t="n">
-        <v>7087578</v>
+        <v>7087556</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,15 +5170,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112194175</v>
+        <v>112194191</v>
       </c>
       <c r="B47" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5611,34 +5181,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518455</v>
+        <v>518083</v>
       </c>
       <c r="R47" t="n">
-        <v>7087371</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5671,6 +5245,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5697,15 +5276,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112194179</v>
+        <v>112194192</v>
       </c>
       <c r="B48" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,34 +5287,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518215</v>
+        <v>518091</v>
       </c>
       <c r="R48" t="n">
-        <v>7087400</v>
+        <v>7087575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5773,6 +5351,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5799,15 +5382,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112194204</v>
+        <v>112194193</v>
       </c>
       <c r="B49" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5815,34 +5393,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>laholmsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518351</v>
+        <v>518252</v>
       </c>
       <c r="R49" t="n">
-        <v>7087447</v>
+        <v>7087576</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5877,6 +5459,11 @@
           <t>2023-09-18</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5898,6 +5485,419 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>112194194</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>laholmsnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>518245</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7087577</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>112194195</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>laholmsnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>518242</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7087613</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>67082926</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brännbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>518269</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7087459</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>67082937</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brännbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>518443</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7087315</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082927</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082944</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194213</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194211</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082909</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194175</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194176</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194177</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194178</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194179</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194180</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194181</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194183</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194184</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194199</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2638,6 +2738,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194201</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194202</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194212</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2937,6 +3052,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082905</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082908</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3139,6 +3264,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082933</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,6 +3370,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082936</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3341,6 +3476,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082942</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3442,6 +3582,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082907</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3543,6 +3688,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082929</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3644,6 +3794,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082940</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3741,6 +3896,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194203</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3838,6 +3998,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194204</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3935,6 +4100,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194205</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4036,6 +4206,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082910</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4137,6 +4312,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082932</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4238,6 +4418,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082941</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4339,6 +4524,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082911</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4440,6 +4630,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082928</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4541,6 +4736,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082945</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4642,6 +4842,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082904</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4741,6 +4946,11 @@
       <c r="AY42" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082946</t>
         </is>
       </c>
     </row>
@@ -4849,6 +5059,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194187</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4955,6 +5170,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194188</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5061,6 +5281,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194189</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5167,6 +5392,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194190</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5273,6 +5503,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194191</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5379,6 +5614,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194192</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5485,6 +5725,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194193</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5591,6 +5836,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194194</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5696,6 +5946,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112194195</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5797,6 +6052,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082926</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,8 +6158,67 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082937</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91435</v>
+        <v>91574</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91574</v>
+        <v>91576</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91576</v>
+        <v>91577</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91577</v>
+        <v>91578</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91579</v>
+        <v>91585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91586</v>
+        <v>91592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91592</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91600</v>
+        <v>91613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54246-2022 artfynd.xlsx
+++ b/artfynd/A 54246-2022 artfynd.xlsx
@@ -2749,7 +2749,7 @@
         <v>112194202</v>
       </c>
       <c r="B22" t="n">
-        <v>91613</v>
+        <v>91614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
